--- a/DateBase/orders/Nha Thu_2026-6-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-19.xlsx
@@ -523,6 +523,9 @@
       <c r="A11" t="str">
         <v>3</v>
       </c>
+      <c r="C11" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nha Thu_2026-6-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-19.xlsx
@@ -526,6 +526,9 @@
       <c r="C11" t="str">
         <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -584,7 +587,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0251555121555200</v>
+        <v>02515551215552015</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -530,9 +530,89 @@
         <v>15</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>237_酷皮_Kupi_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>259_诺拉_Nora_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>84_堪培拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F17" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>15_深紫洋桔梗_Dark Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F18" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>4</v>
+      </c>
+      <c r="C20" t="str">
+        <v>641_绿枫叶_maple leaf_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,7 +667,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02515551215552015</v>
+        <v>02515551215552015564620105550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-19.xlsx
@@ -609,6 +609,9 @@
       <c r="C21" t="str">
         <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -667,7 +670,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02515551215552015564620105550</v>
+        <v>02515551215552015564620105553</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -610,12 +610,92 @@
         <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
       </c>
       <c r="F21" t="str">
-        <v>3</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>458_蓝盆花白色_Scabiosa caucasica white_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>552_蓝盆花紫色_Scabiosa caucasica purple_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>5</v>
+      </c>
+      <c r="C25" t="str" xml:space="preserve">
+        <v xml:space="preserve">416_翠珠紫_Didiscus caeruleus
+blue_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="C26" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>415_百子莲蓝_Agapanthus_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>585_洋牡丹红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>6</v>
+      </c>
+      <c r="C29" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L30"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -670,7 +750,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02515551215552015564620105553</v>
+        <v>02515551215552015564620105553015520153010151530</v>
       </c>
     </row>
   </sheetData>
